--- a/diseases/d122/2015-2019.xlsx
+++ b/diseases/d122/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.01007731314645964</v>
       </c>
@@ -2645,9 +2633,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3041,9 +3026,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3437,9 +3419,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3833,9 +3812,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4229,9 +4205,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4625,9 +4598,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5021,9 +4991,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.01007731314645964</v>
       </c>
@@ -5417,9 +5384,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5813,9 +5777,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6209,9 +6170,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6753,9 +6711,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -7149,9 +7104,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7545,9 +7497,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7941,9 +7890,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -8337,9 +8283,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8733,9 +8676,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -9129,9 +9069,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9525,9 +9462,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9921,9 +9855,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -10317,9 +10248,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10713,9 +10641,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -11109,9 +11034,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -11505,9 +11427,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -12049,9 +11968,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12445,9 +12361,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -12841,9 +12754,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -13237,9 +13147,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13633,9 +13540,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -14029,9 +13933,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14425,9 +14326,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -14821,9 +14719,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -15217,9 +15112,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -15613,9 +15505,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -16009,9 +15898,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -16405,9 +16291,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -16801,9 +16684,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -17345,9 +17225,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -17741,9 +17618,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -18285,9 +18159,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -18681,9 +18552,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -19077,9 +18945,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -19473,9 +19338,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -19869,9 +19731,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -20265,9 +20124,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -20661,9 +20517,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -21353,9 +21206,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -21749,9 +21599,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -22293,9 +22140,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -22687,9 +22531,6 @@
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
